--- a/artfynd/A 43267-2021 artfynd.xlsx
+++ b/artfynd/A 43267-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43267-2021 artfynd.xlsx
+++ b/artfynd/A 43267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95084777</v>
+        <v>95085862</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
+        <v>89388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629966.0908429946</v>
+        <v>630176.1893372714</v>
       </c>
       <c r="R11" t="n">
-        <v>7280786.413041434</v>
+        <v>7280545.108918818</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95085862</v>
+        <v>95085134</v>
       </c>
       <c r="B12" t="n">
-        <v>89388</v>
+        <v>77506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630176.1893372714</v>
+        <v>630346.3043427928</v>
       </c>
       <c r="R12" t="n">
-        <v>7280545.108918818</v>
+        <v>7280769.171087273</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1925,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95085134</v>
+        <v>95085626</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,35 +1941,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630346.3043427928</v>
+        <v>630260.5659183225</v>
       </c>
       <c r="R13" t="n">
-        <v>7280769.171087273</v>
+        <v>7280584.904916829</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,6 +2014,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95085626</v>
+        <v>95085773</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
+        <v>89392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,37 +2061,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630260.5659183225</v>
+        <v>630176.1893372714</v>
       </c>
       <c r="R14" t="n">
-        <v>7280584.904916829</v>
+        <v>7280545.108918818</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2127,11 +2132,6 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95085773</v>
+        <v>95085350</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
+        <v>96354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,39 +2170,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630176.1893372714</v>
+        <v>630396.5082669297</v>
       </c>
       <c r="R15" t="n">
-        <v>7280545.108918818</v>
+        <v>7280592.681654779</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2271,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95085350</v>
+        <v>95085689</v>
       </c>
       <c r="B16" t="n">
-        <v>96354</v>
+        <v>95519</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2313,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630396.5082669297</v>
+        <v>630192.8708647757</v>
       </c>
       <c r="R16" t="n">
-        <v>7280592.681654779</v>
+        <v>7280570.272887323</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2385,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95085689</v>
+        <v>95084922</v>
       </c>
       <c r="B17" t="n">
-        <v>95519</v>
+        <v>89410</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,40 +2398,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630192.8708647757</v>
+        <v>630139.5967557982</v>
       </c>
       <c r="R17" t="n">
-        <v>7280570.272887323</v>
+        <v>7280815.311757462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2499,10 +2499,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95084922</v>
+        <v>95085056</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
+        <v>56395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,35 +2515,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630139.5967557982</v>
+        <v>630234.8952920744</v>
       </c>
       <c r="R18" t="n">
-        <v>7280815.311757462</v>
+        <v>7280805.531216186</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2586,6 +2588,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2619,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95085056</v>
+        <v>95084723</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,37 +2635,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630234.8952920744</v>
+        <v>629950.9304574435</v>
       </c>
       <c r="R19" t="n">
-        <v>7280805.531216186</v>
+        <v>7280791.938552069</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2701,11 +2706,6 @@
       <c r="AB19" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95084723</v>
+        <v>95085770</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
+        <v>89406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,21 +2748,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629950.9304574435</v>
+        <v>630176.1893372714</v>
       </c>
       <c r="R20" t="n">
-        <v>7280791.938552069</v>
+        <v>7280545.108918818</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95085770</v>
+        <v>95086086</v>
       </c>
       <c r="B21" t="n">
-        <v>89406</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630176.1893372714</v>
+        <v>629898.2590146</v>
       </c>
       <c r="R21" t="n">
-        <v>7280545.108918818</v>
+        <v>7280636.481121037</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95086086</v>
+        <v>95086055</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
+        <v>73698</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629898.2590146</v>
+        <v>629905.1460715714</v>
       </c>
       <c r="R22" t="n">
-        <v>7280636.481121037</v>
+        <v>7280621.480522203</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95086055</v>
+        <v>95084828</v>
       </c>
       <c r="B23" t="n">
-        <v>73698</v>
+        <v>81236</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629905.1460715714</v>
+        <v>630039.1557722</v>
       </c>
       <c r="R23" t="n">
-        <v>7280621.480522203</v>
+        <v>7280801.280382044</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3184,10 +3184,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95084828</v>
+        <v>95085089</v>
       </c>
       <c r="B24" t="n">
-        <v>81236</v>
+        <v>77506</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,21 +3200,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630039.1557722</v>
+        <v>630278.7707703876</v>
       </c>
       <c r="R24" t="n">
-        <v>7280801.280382044</v>
+        <v>7280806.264785673</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95085089</v>
+        <v>95086018</v>
       </c>
       <c r="B25" t="n">
         <v>77506</v>
@@ -3338,10 +3338,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630278.7707703876</v>
+        <v>629927.2667996756</v>
       </c>
       <c r="R25" t="n">
-        <v>7280806.264785673</v>
+        <v>7280627.025046708</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3410,10 +3410,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95086018</v>
+        <v>95085499</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3426,21 +3426,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629927.2667996756</v>
+        <v>630250.7923883138</v>
       </c>
       <c r="R26" t="n">
-        <v>7280627.025046708</v>
+        <v>7280581.154752958</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95085499</v>
+        <v>95085087</v>
       </c>
       <c r="B27" t="n">
         <v>89410</v>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630250.7923883138</v>
+        <v>630278.7707703876</v>
       </c>
       <c r="R27" t="n">
-        <v>7280581.154752958</v>
+        <v>7280806.264785673</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3636,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95085087</v>
+        <v>95085132</v>
       </c>
       <c r="B28" t="n">
-        <v>89410</v>
+        <v>89388</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3652,21 +3652,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630278.7707703876</v>
+        <v>630346.3043427928</v>
       </c>
       <c r="R28" t="n">
-        <v>7280806.264785673</v>
+        <v>7280769.171087273</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3749,10 +3749,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95085132</v>
+        <v>95085178</v>
       </c>
       <c r="B29" t="n">
-        <v>89388</v>
+        <v>77506</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3765,21 +3765,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630346.3043427928</v>
+        <v>630427.1164855777</v>
       </c>
       <c r="R29" t="n">
-        <v>7280769.171087273</v>
+        <v>7280713.229513778</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95085178</v>
+        <v>95085207</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
+        <v>77588</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95085207</v>
+        <v>95085923</v>
       </c>
       <c r="B31" t="n">
         <v>77588</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630427.1164855777</v>
+        <v>630079.9866060684</v>
       </c>
       <c r="R31" t="n">
-        <v>7280713.229513778</v>
+        <v>7280565.610947156</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4088,10 +4088,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95085923</v>
+        <v>95085177</v>
       </c>
       <c r="B32" t="n">
-        <v>77588</v>
+        <v>78570</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4104,21 +4104,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630079.9866060684</v>
+        <v>630427.1164855777</v>
       </c>
       <c r="R32" t="n">
-        <v>7280565.610947156</v>
+        <v>7280713.229513778</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95085177</v>
+        <v>95085062</v>
       </c>
       <c r="B33" t="n">
-        <v>78570</v>
+        <v>89388</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630427.1164855777</v>
+        <v>630234.8952920744</v>
       </c>
       <c r="R33" t="n">
-        <v>7280713.229513778</v>
+        <v>7280805.531216186</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4314,10 +4314,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95085062</v>
+        <v>95084852</v>
       </c>
       <c r="B34" t="n">
-        <v>89388</v>
+        <v>81236</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4330,21 +4330,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630234.8952920744</v>
+        <v>630083.876552448</v>
       </c>
       <c r="R34" t="n">
-        <v>7280805.531216186</v>
+        <v>7280801.635229921</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95085927</v>
+        <v>95085082</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
+        <v>56395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4443,35 +4443,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630079.9866060684</v>
+        <v>630278.0369259712</v>
       </c>
       <c r="R35" t="n">
-        <v>7280565.610947156</v>
+        <v>7280804.162967523</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4514,6 +4516,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,10 +4547,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95084852</v>
+        <v>95085339</v>
       </c>
       <c r="B36" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4556,21 +4563,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4581,10 +4588,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630083.876552448</v>
+        <v>630430.0634618226</v>
       </c>
       <c r="R36" t="n">
-        <v>7280801.635229921</v>
+        <v>7280620.262218905</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4653,10 +4660,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95085082</v>
+        <v>95085641</v>
       </c>
       <c r="B37" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4669,37 +4676,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630278.0369259712</v>
+        <v>630260.5659183225</v>
       </c>
       <c r="R37" t="n">
-        <v>7280804.162967523</v>
+        <v>7280584.904916829</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4742,11 +4747,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95085339</v>
+        <v>95085164</v>
       </c>
       <c r="B38" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,21 +4789,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630430.0634618226</v>
+        <v>630436.1369964946</v>
       </c>
       <c r="R38" t="n">
-        <v>7280620.262218905</v>
+        <v>7280715.291142815</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4886,10 +4886,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>95085641</v>
+        <v>95085760</v>
       </c>
       <c r="B39" t="n">
-        <v>77506</v>
+        <v>78603</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4898,25 +4898,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630260.5659183225</v>
+        <v>630175.0143900242</v>
       </c>
       <c r="R39" t="n">
-        <v>7280584.904916829</v>
+        <v>7280562.021493044</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4999,10 +4999,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95085164</v>
+        <v>95084964</v>
       </c>
       <c r="B40" t="n">
-        <v>77506</v>
+        <v>56411</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5015,35 +5015,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630436.1369964946</v>
+        <v>630139.5967557982</v>
       </c>
       <c r="R40" t="n">
-        <v>7280715.291142815</v>
+        <v>7280815.311757462</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5086,6 +5088,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5112,10 +5119,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>95085760</v>
+        <v>95085215</v>
       </c>
       <c r="B41" t="n">
-        <v>78603</v>
+        <v>81236</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5124,25 +5131,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5153,10 +5160,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>630175.0143900242</v>
+        <v>630427.1164855777</v>
       </c>
       <c r="R41" t="n">
-        <v>7280562.021493044</v>
+        <v>7280713.229513778</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5225,10 +5232,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>95084964</v>
+        <v>98310782</v>
       </c>
       <c r="B42" t="n">
-        <v>56411</v>
+        <v>77506</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5241,40 +5248,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Àrdnasåjvvie, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630139.5967557982</v>
+        <v>630428.3247861477</v>
       </c>
       <c r="R42" t="n">
-        <v>7280815.311757462</v>
+        <v>7280769.142604331</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5308,17 +5312,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5333,240 +5332,15 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>95085215</v>
-      </c>
-      <c r="B43" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>630427.1164855777</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7280713.229513778</v>
-      </c>
-      <c r="S43" t="n">
-        <v>25</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>98310782</v>
-      </c>
-      <c r="B44" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Àrdnasåjvvie, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>630428.3247861477</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7280769.142604331</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43267-2021 artfynd.xlsx
+++ b/artfynd/A 43267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95085615</v>
+        <v>95085207</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630250.7923883138</v>
+        <v>630427</v>
       </c>
       <c r="R2" t="n">
-        <v>7280581.154752958</v>
+        <v>7280714</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95085584</v>
+        <v>95085923</v>
       </c>
       <c r="B3" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1506</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630250.7923883138</v>
+        <v>630080</v>
       </c>
       <c r="R3" t="n">
-        <v>7280581.154752958</v>
+        <v>7280566</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95084728</v>
+        <v>95085062</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629965.2640509866</v>
+        <v>630235</v>
       </c>
       <c r="R4" t="n">
-        <v>7280786.375910942</v>
+        <v>7280806</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95085266</v>
+        <v>95085132</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630430.0634618226</v>
+        <v>630346</v>
       </c>
       <c r="R5" t="n">
-        <v>7280620.262218905</v>
+        <v>7280769</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95085912</v>
+        <v>95085862</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630080.0237260211</v>
+        <v>630176</v>
       </c>
       <c r="R6" t="n">
-        <v>7280564.785040027</v>
+        <v>7280545</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95085884</v>
+        <v>95085339</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630125.040276334</v>
+        <v>630430</v>
       </c>
       <c r="R7" t="n">
-        <v>7280549.429481791</v>
+        <v>7280621</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95085988</v>
+        <v>95085615</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,37 +1274,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629959.5341056102</v>
+        <v>630251</v>
       </c>
       <c r="R8" t="n">
-        <v>7280600.336823495</v>
+        <v>7280581</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,24 +1332,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95085023</v>
+        <v>95085773</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,21 +1372,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630212.8553721544</v>
+        <v>630176</v>
       </c>
       <c r="R9" t="n">
-        <v>7280807.43573746</v>
+        <v>7280545</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,19 +1430,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,37 +1459,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95085159</v>
+        <v>95085770</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1627,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630376.0669263243</v>
+        <v>630176</v>
       </c>
       <c r="R10" t="n">
-        <v>7280724.583725988</v>
+        <v>7280545</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,19 +1528,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95085862</v>
+        <v>95084828</v>
       </c>
       <c r="B11" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630176.1893372714</v>
+        <v>630039</v>
       </c>
       <c r="R11" t="n">
-        <v>7280545.108918818</v>
+        <v>7280802</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,19 +1626,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,15 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95085134</v>
+        <v>95084852</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,21 +1666,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630346.3043427928</v>
+        <v>630084</v>
       </c>
       <c r="R12" t="n">
-        <v>7280769.171087273</v>
+        <v>7280802</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1886,19 +1724,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,15 +1753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95085626</v>
+        <v>95085215</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,37 +1764,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630260.5659183225</v>
+        <v>630427</v>
       </c>
       <c r="R13" t="n">
-        <v>7280584.904916829</v>
+        <v>7280714</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,24 +1822,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,15 +1851,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95085773</v>
+        <v>95086055</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,21 +1862,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630176.1893372714</v>
+        <v>629906</v>
       </c>
       <c r="R14" t="n">
-        <v>7280545.108918818</v>
+        <v>7280621</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,19 +1920,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,52 +1949,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95085350</v>
+        <v>95085584</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630396.5082669297</v>
+        <v>630251</v>
       </c>
       <c r="R15" t="n">
-        <v>7280592.681654779</v>
+        <v>7280581</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2233,19 +2018,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,52 +2047,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95085689</v>
+        <v>95085177</v>
       </c>
       <c r="B16" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630192.8708647757</v>
+        <v>630427</v>
       </c>
       <c r="R16" t="n">
-        <v>7280570.272887323</v>
+        <v>7280714</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2347,19 +2116,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,37 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95084922</v>
+        <v>95084723</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2427,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630139.5967557982</v>
+        <v>629951</v>
       </c>
       <c r="R17" t="n">
-        <v>7280815.311757462</v>
+        <v>7280792</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,19 +2214,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,53 +2243,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95085056</v>
+        <v>95084728</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630234.8952920744</v>
+        <v>629965</v>
       </c>
       <c r="R18" t="n">
-        <v>7280805.531216186</v>
+        <v>7280786</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2575,24 +2312,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,19 +2341,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95084723</v>
+        <v>95084777</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2660,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629950.9304574435</v>
+        <v>629966</v>
       </c>
       <c r="R19" t="n">
-        <v>7280791.938552069</v>
+        <v>7280786</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2693,19 +2410,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,37 +2439,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95085770</v>
+        <v>95084995</v>
       </c>
       <c r="B20" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2773,10 +2475,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630176.1893372714</v>
+        <v>630213</v>
       </c>
       <c r="R20" t="n">
-        <v>7280545.108918818</v>
+        <v>7280807</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2806,19 +2508,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,19 +2537,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95086086</v>
+        <v>95085089</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2886,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629898.2590146</v>
+        <v>630278</v>
       </c>
       <c r="R21" t="n">
-        <v>7280636.481121037</v>
+        <v>7280806</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2919,19 +2606,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2958,37 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95086055</v>
+        <v>95085134</v>
       </c>
       <c r="B22" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2999,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629905.1460715714</v>
+        <v>630346</v>
       </c>
       <c r="R22" t="n">
-        <v>7280621.480522203</v>
+        <v>7280769</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3032,19 +2704,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3071,37 +2733,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95084828</v>
+        <v>95085164</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3112,10 +2769,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630039.1557722</v>
+        <v>630436</v>
       </c>
       <c r="R23" t="n">
-        <v>7280801.280382044</v>
+        <v>7280715</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3145,19 +2802,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,19 +2831,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95085089</v>
+        <v>95085178</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3225,10 +2867,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630278.7707703876</v>
+        <v>630427</v>
       </c>
       <c r="R24" t="n">
-        <v>7280806.264785673</v>
+        <v>7280714</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3258,19 +2900,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,19 +2929,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95086018</v>
+        <v>95085641</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3338,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629927.2667996756</v>
+        <v>630261</v>
       </c>
       <c r="R25" t="n">
-        <v>7280627.025046708</v>
+        <v>7280585</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3371,19 +2998,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,37 +3027,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95085499</v>
+        <v>95085912</v>
       </c>
       <c r="B26" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3063,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630250.7923883138</v>
+        <v>630080</v>
       </c>
       <c r="R26" t="n">
-        <v>7280581.154752958</v>
+        <v>7280564</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3484,19 +3096,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,37 +3125,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95085087</v>
+        <v>95085927</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3564,10 +3161,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630278.7707703876</v>
+        <v>630080</v>
       </c>
       <c r="R27" t="n">
-        <v>7280806.264785673</v>
+        <v>7280566</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,19 +3194,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,37 +3223,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95085132</v>
+        <v>95086018</v>
       </c>
       <c r="B28" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630346.3043427928</v>
+        <v>629927</v>
       </c>
       <c r="R28" t="n">
-        <v>7280769.171087273</v>
+        <v>7280627</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,19 +3292,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,19 +3321,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95085178</v>
+        <v>95086086</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3790,10 +3357,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630427.1164855777</v>
+        <v>629898</v>
       </c>
       <c r="R29" t="n">
-        <v>7280713.229513778</v>
+        <v>7280636</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3823,19 +3390,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,54 +3419,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95085207</v>
+        <v>98310782</v>
       </c>
       <c r="B30" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Àrdnasåjvvie, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630427.1164855777</v>
+        <v>630428</v>
       </c>
       <c r="R30" t="n">
-        <v>7280713.229513778</v>
+        <v>7280769</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3933,22 +3484,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,49 +3504,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95085923</v>
+        <v>95085760</v>
       </c>
       <c r="B31" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4016,10 +3552,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630079.9866060684</v>
+        <v>630175</v>
       </c>
       <c r="R31" t="n">
-        <v>7280565.610947156</v>
+        <v>7280562</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4049,19 +3585,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,37 +3614,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95085177</v>
+        <v>95085884</v>
       </c>
       <c r="B32" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4129,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630427.1164855777</v>
+        <v>630125</v>
       </c>
       <c r="R32" t="n">
-        <v>7280713.229513778</v>
+        <v>7280550</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4162,19 +3683,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4201,51 +3712,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95085062</v>
+        <v>95084964</v>
       </c>
       <c r="B33" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630234.8952920744</v>
+        <v>630140</v>
       </c>
       <c r="R33" t="n">
-        <v>7280805.531216186</v>
+        <v>7280815</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4275,19 +3783,14 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4314,15 +3817,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>95084852</v>
+        <v>95085056</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,35 +3828,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630083.876552448</v>
+        <v>630235</v>
       </c>
       <c r="R34" t="n">
-        <v>7280801.635229921</v>
+        <v>7280806</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4388,19 +3888,14 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,12 +3925,7 @@
         <v>95085082</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4470,10 +3960,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630278.0369259712</v>
+        <v>630278</v>
       </c>
       <c r="R35" t="n">
-        <v>7280804.162967523</v>
+        <v>7280805</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4503,19 +3993,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4547,15 +4027,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>95085339</v>
+        <v>95085626</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,35 +4038,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630430.0634618226</v>
+        <v>630261</v>
       </c>
       <c r="R36" t="n">
-        <v>7280620.262218905</v>
+        <v>7280585</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4621,19 +4098,14 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4660,15 +4132,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>95085641</v>
+        <v>95085988</v>
       </c>
       <c r="B37" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4676,35 +4143,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630260.5659183225</v>
+        <v>629959</v>
       </c>
       <c r="R37" t="n">
-        <v>7280584.904916829</v>
+        <v>7280601</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4734,19 +4203,14 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,15 +4237,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>95085164</v>
+        <v>98310784</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4789,38 +4248,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Àrdnasåjvvie, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630436.1369964946</v>
+        <v>630407</v>
       </c>
       <c r="R38" t="n">
-        <v>7280715.291142815</v>
+        <v>7280620</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4844,22 +4302,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4874,27 +4322,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>95085760</v>
+        <v>95085689</v>
       </c>
       <c r="B39" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4902,35 +4345,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630175.0143900242</v>
+        <v>630193</v>
       </c>
       <c r="R39" t="n">
-        <v>7280562.021493044</v>
+        <v>7280571</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4960,19 +4404,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4999,53 +4433,47 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>95084964</v>
+        <v>95085350</v>
       </c>
       <c r="B40" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630139.5967557982</v>
+        <v>630396</v>
       </c>
       <c r="R40" t="n">
-        <v>7280815.311757462</v>
+        <v>7280593</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5075,24 +4503,9 @@
           <t>2021-07-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,231 +4529,6 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>95085215</v>
-      </c>
-      <c r="B41" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>630427.1164855777</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7280713.229513778</v>
-      </c>
-      <c r="S41" t="n">
-        <v>25</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2021-07-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>98310782</v>
-      </c>
-      <c r="B42" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Àrdnasåjvvie, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>630428.3247861477</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7280769.142604331</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43267-2021 artfynd.xlsx
+++ b/artfynd/A 43267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085923</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085062</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085132</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085862</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085339</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085773</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085770</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084828</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,6 +1805,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084852</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085215</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95086055</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085584</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085177</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084723</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084728</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084995</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085089</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085134</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2828,6 +2938,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085164</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085178</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,6 +3144,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085641</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085912</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085927</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95086018</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95086086</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310782</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3611,6 +3761,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085760</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085884</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3814,6 +3974,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95084964</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3919,6 +4084,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085056</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4024,6 +4194,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085082</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085626</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4234,6 +4414,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085988</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4331,6 +4516,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310784</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4430,6 +4620,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085689</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4529,8 +4724,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95085350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>